--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:09:43+00:00</t>
+    <t>2026-07-13T09:21:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:21:26+00:00</t>
+    <t>2026-07-13T09:30:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T09:30:27+00:00</t>
+    <t>2026-07-14T07:23:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -8,12 +8,13 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include #0" r:id="rId4" sheetId="2"/>
+    <sheet name="Include #1" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="60" uniqueCount="58">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
   <si>
     <t>Property</t>
   </si>
@@ -60,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T07:23:58+00:00</t>
+    <t>2026-07-17T09:40:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -180,6 +181,24 @@
     <t>Plan of care note</t>
   </si>
   <si>
+    <t>75310-3</t>
+  </si>
+  <si>
+    <t>Health concerns Document</t>
+  </si>
+  <si>
+    <t>48765-2</t>
+  </si>
+  <si>
+    <t>Allergies and adverse reactions Document</t>
+  </si>
+  <si>
+    <t>46240-8</t>
+  </si>
+  <si>
+    <t>History of Hospitalizations+Outpatient visits Narrative</t>
+  </si>
+  <si>
     <t/>
   </si>
   <si>
@@ -187,6 +206,15 @@
   </si>
   <si>
     <t>http://loinc.org</t>
+  </si>
+  <si>
+    <t>866144008</t>
+  </si>
+  <si>
+    <t>Encounter note (record artifact)</t>
+  </si>
+  <si>
+    <t>http://snomed.info/sct</t>
   </si>
 </sst>
 </file>
@@ -450,7 +478,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B16"/>
+  <dimension ref="A1:B19"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -574,15 +602,85 @@
         <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B16" t="s" s="2">
-        <v>57</v>
+        <v>58</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="s" s="2">
+        <v>59</v>
+      </c>
+      <c r="B17" t="s" s="2">
+        <v>60</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B18" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B19" t="s" s="2">
+        <v>63</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr defaultRowHeight="15.0"/>
+  <cols>
+    <col min="1" max="1" width="30.703125" customWidth="true"/>
+    <col min="2" max="2" width="50.703125" customWidth="true"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="s" s="1">
+        <v>28</v>
+      </c>
+      <c r="B1" t="s" s="1">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="s" s="2">
+        <v>64</v>
+      </c>
+      <c r="B2" t="s" s="2">
+        <v>65</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="s" s="2">
+        <v>61</v>
+      </c>
+      <c r="B3" t="s" s="2">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="s" s="2">
+        <v>62</v>
+      </c>
+      <c r="B4" t="s" s="2">
+        <v>66</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T09:40:30+00:00</t>
+    <t>2026-07-21T08:04:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -25,7 +25,7 @@
     <t>URL</t>
   </si>
   <si>
-    <t>http://tecnomod-um.org/ValueSet/resq-stroke-discharge-section-code-vs</t>
+    <t>http://qualityregistry.org/ValueSet/resq-stroke-discharge-section-code-vs</t>
   </si>
   <si>
     <t>Version</t>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-21T08:04:16+00:00</t>
+    <t>2026-08-31T09:17:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -73,7 +73,7 @@
     <t>Contact</t>
   </si>
   <si>
-    <t>Tecnomod / Universidad de Murcia (http://tecnomod-um.org)</t>
+    <t>Tecnomod / Universidad de Murcia (http://qualityregistry.org)</t>
   </si>
   <si>
     <t>Jurisdiction</t>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T09:17:06+00:00</t>
+    <t>2026-08-31T10:08:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="68" uniqueCount="61">
   <si>
     <t>Property</t>
   </si>
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-31T10:08:26+00:00</t>
+    <t>2026-09-04T09:44:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -85,7 +85,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Allowed LOINC section codes for the RESQ Stroke Hospital Discharge Summary Composition.</t>
+    <t>Allowed section codes for the RESQ Stroke Discharge Patient Summary Composition.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -181,24 +181,6 @@
     <t>Plan of care note</t>
   </si>
   <si>
-    <t>75310-3</t>
-  </si>
-  <si>
-    <t>Health concerns Document</t>
-  </si>
-  <si>
-    <t>48765-2</t>
-  </si>
-  <si>
-    <t>Allergies and adverse reactions Document</t>
-  </si>
-  <si>
-    <t>46240-8</t>
-  </si>
-  <si>
-    <t>History of Hospitalizations+Outpatient visits Narrative</t>
-  </si>
-  <si>
     <t/>
   </si>
   <si>
@@ -208,13 +190,13 @@
     <t>http://loinc.org</t>
   </si>
   <si>
-    <t>866144008</t>
-  </si>
-  <si>
-    <t>Encounter note (record artifact)</t>
-  </si>
-  <si>
-    <t>http://snomed.info/sct</t>
+    <t>treatment-timings</t>
+  </si>
+  <si>
+    <t>Treatment Timings</t>
+  </si>
+  <si>
+    <t>http://qualityregistry.org/CodeSystem/stroke-discharge-summary-section-cs</t>
   </si>
 </sst>
 </file>
@@ -478,7 +460,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B19"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -602,39 +584,15 @@
         <v>55</v>
       </c>
       <c r="B15" t="s" s="2">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="s" s="2">
+        <v>56</v>
+      </c>
+      <c r="B16" t="s" s="2">
         <v>57</v>
-      </c>
-      <c r="B16" t="s" s="2">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="s" s="2">
-        <v>59</v>
-      </c>
-      <c r="B17" t="s" s="2">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="s" s="2">
-        <v>61</v>
-      </c>
-      <c r="B18" t="s" s="2">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="s" s="2">
-        <v>62</v>
-      </c>
-      <c r="B19" t="s" s="2">
-        <v>63</v>
       </c>
     </row>
   </sheetData>
@@ -661,26 +619,26 @@
     </row>
     <row r="2">
       <c r="A2" t="s" s="2">
-        <v>64</v>
+        <v>58</v>
       </c>
       <c r="B2" t="s" s="2">
-        <v>65</v>
+        <v>59</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="s" s="2">
-        <v>61</v>
+        <v>55</v>
       </c>
       <c r="B3" t="s" s="2">
-        <v>61</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>62</v>
+        <v>56</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>66</v>
+        <v>60</v>
       </c>
     </row>
   </sheetData>

--- a/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
+++ b/ValueSet-resq-stroke-discharge-section-code-vs.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-04T09:44:50+00:00</t>
+    <t>2026-09-04T10:11:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
